--- a/test-data/Sample_Accounts (1).xlsx
+++ b/test-data/Sample_Accounts (1).xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">Account Name</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t xml:space="preserve">Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sophia </t>
   </si>
   <si>
     <t xml:space="preserve">Ronaldo@gmail.com</t>
@@ -124,6 +121,7 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -493,32 +491,30 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>13</v>
-      </c>
+      <c r="A2" s="3"/>
       <c r="B2" s="1" t="n">
         <v>875485456789</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="K2" s="1" t="n">
         <v>421304</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
